--- a/data/INDEX-MAIN.xlsx
+++ b/data/INDEX-MAIN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivaan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivaan\Downloads\RAJLIVEPRICEBOOK-main\RAJLIVEPRICEBOOK-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B159FF1-36F0-4AA3-ACDB-601ADEA9575C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD24D2A-7050-4C12-89F5-3E4CC8E83D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="MAIN INDEX" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MAIN INDEX'!$A$2:$C$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MAIN INDEX'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="186">
   <si>
     <t>SR</t>
   </si>
@@ -530,6 +531,69 @@
   </si>
   <si>
     <t>BELTS, METALS &amp; KITS, TENSIONER</t>
+  </si>
+  <si>
+    <t>COSMO</t>
+  </si>
+  <si>
+    <t>GEEKAY</t>
+  </si>
+  <si>
+    <t>GOLD BOSS</t>
+  </si>
+  <si>
+    <t>OXMO</t>
+  </si>
+  <si>
+    <t>REFEX</t>
+  </si>
+  <si>
+    <t>TIMING GOLD</t>
+  </si>
+  <si>
+    <t>TVS</t>
+  </si>
+  <si>
+    <t>VIGEX</t>
+  </si>
+  <si>
+    <t>WAGNER</t>
+  </si>
+  <si>
+    <t>BHARATI POWER</t>
+  </si>
+  <si>
+    <t>Hydrualic Jack</t>
+  </si>
+  <si>
+    <t>Hydrualic Filter, Diesel Filter</t>
+  </si>
+  <si>
+    <t>HEXAGONAL HEAD BOLT</t>
+  </si>
+  <si>
+    <t>JACK ROD</t>
+  </si>
+  <si>
+    <t>ACUATOR</t>
+  </si>
+  <si>
+    <t>TETRAFLUROETHANE GAS CAN</t>
+  </si>
+  <si>
+    <t>HADWARE ADJUSTER</t>
+  </si>
+  <si>
+    <t>4T-PLUS OIL, TRACTOR POWER OIL, SYNTH 4T-PLUS OIL</t>
+  </si>
+  <si>
+    <t>EPDM HOSE, AIR BRAKE PIPE, BANJO PIPE, OIL PUMP PIPE, COOLANT PIPE</t>
+  </si>
+  <si>
+    <t>CONDENSER</t>
+  </si>
+  <si>
+    <t>BRAKE PARTS,ROTOR, ADJUSTER &amp; OTHER PARTS</t>
   </si>
 </sst>
 </file>
@@ -575,29 +639,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Cambria"/>
@@ -608,6 +649,29 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="1"/>
       <scheme val="major"/>
@@ -627,7 +691,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -663,6 +727,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -681,32 +756,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1020,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
@@ -1029,937 +1106,1058 @@
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.5">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" ht="16.5">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="14"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="11">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A4" s="11">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="11">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="11">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="11">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="11">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="11">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="11">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="11">
+      <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A12" s="11">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row r="13" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A13" s="11">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="s">
+    <row r="14" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C14" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A14" s="11">
-        <v>12</v>
-      </c>
-      <c r="B14" s="5" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C15" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="11">
+    <row r="16" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A21" s="6">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="6">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A26" s="6">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A27" s="6">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A28" s="6">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A29" s="6">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A30" s="6">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A31" s="6">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A32" s="6">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A33" s="6">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A34" s="6">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A35" s="6">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A36" s="6">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A37" s="6">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A38" s="6">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A39" s="6">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A40" s="6">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A41" s="6">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A42" s="6">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A43" s="6">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A44" s="6">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A45" s="6">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A46" s="6">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A48" s="6">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A49" s="6">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A50" s="6">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A51" s="6">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A52" s="6">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A53" s="6">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A54" s="6">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A55" s="6">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A56" s="6">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A57" s="6">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A58" s="6">
+        <v>56</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A59" s="6">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A16" s="11">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A17" s="11">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="11">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A19" s="11">
+    </row>
+    <row r="60" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A60" s="6">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A61" s="6">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A62" s="6">
+        <v>60</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A63" s="6">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A64" s="6">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="6">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A66" s="6">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="6">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="6">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A69" s="6">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A70" s="6">
+        <v>68</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A71" s="6">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A72" s="6">
+        <v>70</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="6">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="6">
+        <v>72</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A75" s="6">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A76" s="6">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A77" s="6">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A78" s="6">
+        <v>76</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A79" s="6">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A80" s="6">
+        <v>78</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A81" s="6">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A82" s="6">
+        <v>80</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A83" s="6">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A84" s="6">
+        <v>82</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="17.100000000000001" customHeight="1">
+      <c r="A85" s="6">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="6">
+        <v>84</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="6">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="6">
+        <v>86</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="6">
+        <v>87</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="6">
+        <v>88</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="6">
+        <v>89</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="6">
+        <v>90</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="6">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A20" s="11">
-        <v>18</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A21" s="11">
-        <v>19</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="11">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="11">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="24">
-      <c r="A24" s="11">
-        <v>22</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A25" s="11">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A26" s="11">
-        <v>24</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A27" s="11">
-        <v>25</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A28" s="11">
-        <v>26</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A29" s="11">
-        <v>27</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A30" s="11">
-        <v>28</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A31" s="11">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5" t="s">
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="6">
+        <v>92</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="6">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="6">
         <v>94</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A32" s="11">
-        <v>30</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A33" s="11">
-        <v>31</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A34" s="11">
-        <v>32</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A35" s="11">
-        <v>33</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A36" s="11">
-        <v>34</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A37" s="11">
-        <v>35</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A38" s="11">
-        <v>36</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A39" s="11">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A40" s="11">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A41" s="11">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A42" s="11">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A43" s="11">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A44" s="11">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A45" s="11">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A46" s="11">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="11">
-        <v>45</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A48" s="11">
-        <v>46</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A49" s="11">
-        <v>47</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A50" s="11">
-        <v>48</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A51" s="11">
-        <v>49</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A52" s="11">
-        <v>50</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A53" s="11">
-        <v>51</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A54" s="11">
-        <v>52</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A55" s="11">
-        <v>53</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A56" s="11">
-        <v>54</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A57" s="11">
-        <v>55</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A58" s="11">
-        <v>56</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A59" s="11">
-        <v>57</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A60" s="11">
-        <v>58</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A61" s="11">
-        <v>59</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A62" s="11">
-        <v>60</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A63" s="11">
-        <v>61</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A64" s="11">
-        <v>62</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="11">
-        <v>63</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A66" s="11">
-        <v>64</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="11">
-        <v>65</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="11">
-        <v>66</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A69" s="11">
-        <v>67</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A70" s="11">
-        <v>68</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A71" s="11">
-        <v>69</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A72" s="11">
-        <v>70</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="11">
-        <v>71</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="11">
-        <v>72</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A75" s="11">
-        <v>73</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A76" s="11">
-        <v>74</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A77" s="11">
-        <v>75</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A78" s="11">
-        <v>76</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A79" s="11">
-        <v>77</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A80" s="11">
-        <v>78</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A81" s="11">
-        <v>79</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A82" s="11">
-        <v>80</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A83" s="11">
-        <v>81</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A84" s="11">
-        <v>82</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="17.100000000000001" customHeight="1">
-      <c r="A85" s="11">
-        <v>83</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>93</v>
+      <c r="B96" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
